--- a/docs/analisis-requisitos/HU-CPA-4250-PARTE-PUBLICA-CATEGORIAS-CPA-VIRTUAL_V0.xlsx
+++ b/docs/analisis-requisitos/HU-CPA-4250-PARTE-PUBLICA-CATEGORIAS-CPA-VIRTUAL_V0.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_CPA_Virtual\HU\SP1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_CPA_Virtual\HU\SP7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FF50384-D668-4FE6-9C6C-E12510758209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91D0F24F-11AD-4941-BA78-3BD1C8F2EE74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="204" xr2:uid="{611E275B-AF68-4D54-8B4F-28D93EBAB353}"/>
   </bookViews>
@@ -83,24 +83,12 @@
     <t>Cabecera</t>
   </si>
   <si>
-    <t>Imagen Categoria</t>
-  </si>
-  <si>
-    <t>Detalle Categoria</t>
-  </si>
-  <si>
     <t>Filtros búsqueda</t>
   </si>
   <si>
-    <t>Filtro Tipo Categoría</t>
-  </si>
-  <si>
     <t>Se mostrará el valor seleccionado.</t>
   </si>
   <si>
-    <t>Listado Categorías</t>
-  </si>
-  <si>
     <t>Botón Volver</t>
   </si>
   <si>
@@ -161,63 +149,43 @@
     <t>Cualquier usuario tendrá acceso a la parte pública con información relacionada de las distintas categorías de talleres, actividades y servicios existentes en los distintos CPAs.</t>
   </si>
   <si>
-    <t>Si el tipo de categoría seleccionado es 'Taller', se pasará al formulario detallado en la HU-CPA-4280-PARTE-PUBLICA-TALLERES-CPA-VIRTUAL).
-Si el tipo de categoría seleccionado es 'Actividad', se pasará al formulario detallado en la HU-CPA-4290-PARTE-PUBLICA-ACTIVIDADES-CPA-VIRTUAL).
-Si el tipo de categoría seleccionado es 'Servicio', se pasará al formulario detallado en la HU-CPA-4295-PARTE-PUBLICA-SERVICIOS-CPA-VIRTUAL).</t>
+    <t>Si se selecciona una categoría del listado y se decide pulsar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cada una de las categorías de (talleres, actividades o servicios), presentará una tipo categoría, nombre categoria, imagen </t>
+  </si>
+  <si>
+    <t>Como usuario que accede a la parte pública del aplicativo CPA Virtual, desde el Formulario Acceso Parte Pública (HU-CPA-3100-ACCESO-PARTE-PUBLICA-CPA-VIRTUAL_V0), tras haber pulsado desde el apartado 'Accesos Directos' al enlace de Talleres, Actividades y Servicios</t>
+  </si>
+  <si>
+    <t>Campo texto. No editable. En función de que el acceso a la pantalla sea desde 'Talleres', 'Actividades' o 'Servicios' el valor por defecto será 'Talleres' ,  'Actividades' o 'Servicios', según corresponda.</t>
+  </si>
+  <si>
+    <t>Botón Aplicar</t>
+  </si>
+  <si>
+    <t>Se presenta en el formulario el botón Aplicar</t>
+  </si>
+  <si>
+    <t>Se mostrará el valor obtenido previamente.</t>
+  </si>
+  <si>
+    <t>Si el tipo de categoría seleccionado es 'Talleres', se pasará al formulario detallado en la HU-CPA-4280-PARTE-PUBLICA-TALLERES-CPA-VIRTUAL).
+Si el tipo de categoría seleccionado es 'Actividades', se pasará al formulario detallado en la HU-CPA-4290-PARTE-PUBLICA-ACTIVIDADES-CPA-VIRTUAL).
+Si el tipo de categoría seleccionado es 'Servicios', se pasará al formulario detallado en la HU-CPA-4295-PARTE-PUBLICA-SERVICIOS-CPA-VIRTUAL).</t>
+  </si>
+  <si>
+    <t>Imagen Tematica</t>
+  </si>
+  <si>
+    <t>Detalle Tematica</t>
+  </si>
+  <si>
+    <t>Filtro Tipo Tematica</t>
   </si>
   <si>
     <r>
-      <t>Se presentará información relacionada con las categorías de talleres, actividades y servicios definidas para los distintos CPAs.
-Mediante la operación '</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>consultarDefinicionCategoría</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>' que accederá al tipo de contenido 'Conceptos' del repositorio Drupal, se presentará en pantalla la imagen y definición de lo que se entiende por categoría de taller, actividad o servicio.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Se presenta en pantalla el valor obtenido mediante la operación '</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>consultarDefinicionCategoría</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>'.</t>
-    </r>
-  </si>
-  <si>
-    <t>Si se selecciona una categoría del listado y se decide pulsar.</t>
-  </si>
-  <si>
-    <r>
-      <t>Si el tipo de categoría seleccionado es 'Taller', mediante la operación '</t>
+      <t>Si el tipo de categoría seleccionado es 'Talleres', mediante la operación '</t>
     </r>
     <r>
       <rPr>
@@ -235,8 +203,8 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> que accederá a los tipos de contenido 'Categorias', 'TalleresCentro', 'Centros', 'Provincias', 'Municipios' y 'Localidades' se obtendrá una relación de todas aquellas Categorías de Talleres que tengan un Taller en alguno de los centros, coincidentes con los criterios definidos en los filtros de búsqueda.
-Si el tipo de categoría seleccionado es 'Actividad', mediante la operación '</t>
+      <t xml:space="preserve"> que accederá a los tipos de contenido 'Tematicas', 'TalleresCentro', 'Centros', 'Provincias', 'Municipios' y 'Localidades' se obtendrá una relación de todas aquellas Categorías de Talleres que tengan un Taller en alguno de los centros, coincidentes con los criterios definidos en los filtros de búsqueda.
+Si el tipo de categoría seleccionado es 'Actividades', mediante la operación '</t>
     </r>
     <r>
       <rPr>
@@ -254,8 +222,8 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>' que accederá a los tipos de contenido 'Categorias', 'ActividadesCentro', 'Centros', 'Provincias', 'Municipios' y 'Localidades' se obtendrá una relación de todas aquellas Categorías de Actividades que tengan una actividad en alguno de los centros, coincidentes con los criterios definidos en los filtros de búsqueda.
-Si el tipo de categoría seleccionado es 'Servicio', mediante la operación '</t>
+      <t>' que accederá a los tipos de contenido 'Tematicas', 'ActividadesCentro', 'Centros', 'Provincias', 'Municipios' y 'Localidades' se obtendrá una relación de todas aquellas Categorías de Actividades que tengan una actividad en alguno de los centros, coincidentes con los criterios definidos en los filtros de búsqueda.
+Si el tipo de categoría seleccionado es 'Servicios', mediante la operación '</t>
     </r>
     <r>
       <rPr>
@@ -273,39 +241,87 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>' que accederá a los tipos de contenido 'Categorias', 'ServiciosCentro', 'Centros', 'Provincias', 'Municipios' y 'Localidades' se obtendrá una relación de todas aquellos Categorías de Servicios que tengan un servicio en alguno de los centros, coincidentes con los criterios definidos en los filtros de búsqueda.</t>
+      <t>' que accederá a los tipos de contenido 'Tematicas', 'ServiciosCentro', 'Centros', 'Provincias', 'Municipios' y 'Localidades' se obtendrá una relación de todas aquellos Categorías de Servicios que tengan un servicio en alguno de los centros, coincidentes con los criterios definidos en los filtros de búsqueda.</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Cada una de las categorías de (talleres, actividades o servicios), presentará una tipo categoría, nombre categoria, imagen </t>
-  </si>
-  <si>
-    <t>Como usuario que accede a la parte pública del aplicativo CPA Virtual, desde el Formulario Acceso Parte Pública (HU-CPA-3100-ACCESO-PARTE-PUBLICA-CPA-VIRTUAL_V0), tras haber pulsado desde el apartado 'Accesos Directos' al enlace de Talleres, Actividades y Servicios</t>
-  </si>
-  <si>
-    <t>Campo texto. No editable. En función de que el acceso a la pantalla sea desde 'Talleres', 'Actividades' o 'Servicios' el valor por defecto será 'Talleres' ,  'Actividades' o 'Servicios', según corresponda.</t>
-  </si>
-  <si>
-    <t>Botón Aplicar</t>
-  </si>
-  <si>
-    <t>Se presenta en el formulario el botón Aplicar</t>
-  </si>
-  <si>
-    <t>Se mostrará el valor obtenido previamente.</t>
-  </si>
-  <si>
-    <t>tipo categoria</t>
-  </si>
-  <si>
-    <t>nombre categoria</t>
+    <t>Listado Tematicas</t>
+  </si>
+  <si>
+    <t>tipo Tematica</t>
+  </si>
+  <si>
+    <t>Denominación Tematica</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Se presentará información relacionada con las categorías de talleres, actividades y servicios definidas para los distintos CPAs.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Mediante la operación '</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>consultarDefinicionCategoría</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>' que accederá al tipo de contenido 'Conceptos' del repositorio Drupal, se presentará en pantalla la imagen y definición de lo que se entiende por categoría de taller, actividad o servicio.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Se presenta en pantalla el valor obtenido mediante la operación '</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>consultarDefinicionCategoría</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>'.</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -328,6 +344,21 @@
       <b/>
       <sz val="10"/>
       <color indexed="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <strike/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -416,7 +447,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -437,6 +468,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -466,17 +503,17 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>349483</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>70009</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>641350</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>82263</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Imagen 1">
+        <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{70F1E208-6F54-8526-B42A-3A6BDACDB48C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40058AE9-0B96-42A2-8BEE-0C114B0F0F95}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -493,7 +530,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="4534133" cy="3086259"/>
+          <a:ext cx="2997200" cy="3574763"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -919,31 +956,31 @@
     </row>
     <row r="26" spans="1:9" ht="113" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E26" s="2">
         <v>1</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -951,33 +988,33 @@
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="3" t="s">
+      <c r="E27" s="8"/>
+      <c r="F27" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
     </row>
     <row r="28" spans="1:9" ht="38" x14ac:dyDescent="0.25">
       <c r="A28" s="7"/>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
-      <c r="E28" s="2">
+      <c r="E28" s="8">
         <v>2</v>
       </c>
-      <c r="F28" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G28" s="3" t="s">
+      <c r="F28" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="G28" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="H28" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>44</v>
+      <c r="H28" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="38" x14ac:dyDescent="0.25">
@@ -985,20 +1022,20 @@
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
-      <c r="E29" s="2">
+      <c r="E29" s="8">
         <v>3</v>
       </c>
-      <c r="F29" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G29" s="3" t="s">
+      <c r="F29" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="G29" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="H29" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>44</v>
+      <c r="H29" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -1008,7 +1045,7 @@
       <c r="D30" s="7"/>
       <c r="E30" s="2"/>
       <c r="F30" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
@@ -1023,16 +1060,16 @@
         <v>6</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="25" x14ac:dyDescent="0.25">
@@ -1044,16 +1081,16 @@
         <v>7</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="25" x14ac:dyDescent="0.25">
@@ -1065,16 +1102,16 @@
         <v>8</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="25" x14ac:dyDescent="0.25">
@@ -1086,16 +1123,16 @@
         <v>9</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="25" x14ac:dyDescent="0.25">
@@ -1107,16 +1144,16 @@
         <v>10</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="25" x14ac:dyDescent="0.25">
@@ -1128,16 +1165,16 @@
         <v>11</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="25" x14ac:dyDescent="0.25">
@@ -1149,16 +1186,16 @@
         <v>12</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="25" x14ac:dyDescent="0.25">
@@ -1170,16 +1207,16 @@
         <v>13</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="25" x14ac:dyDescent="0.25">
@@ -1191,16 +1228,16 @@
         <v>14</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="25" x14ac:dyDescent="0.25">
@@ -1212,16 +1249,16 @@
         <v>15</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="376.5" x14ac:dyDescent="0.25">
@@ -1233,16 +1270,16 @@
         <v>16</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>11</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="150" x14ac:dyDescent="0.25">
@@ -1254,16 +1291,16 @@
         <v>17</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="H42" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I42" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
@@ -1273,7 +1310,7 @@
       <c r="D43" s="7"/>
       <c r="E43" s="2"/>
       <c r="F43" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>14</v>
@@ -1282,17 +1319,17 @@
         <v>12</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="25" x14ac:dyDescent="0.25">
       <c r="A44" s="7"/>
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
       <c r="D44" s="7"/>
       <c r="E44" s="2"/>
       <c r="F44" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>14</v>
@@ -1301,7 +1338,7 @@
         <v>12</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="37.5" x14ac:dyDescent="0.25">
@@ -1313,16 +1350,16 @@
         <v>18</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>11</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
